--- a/verification_forms/026_trust_service_provider_identity_verification_form--verification_forms.xlsx
+++ b/verification_forms/026_trust_service_provider_identity_verification_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bank'}</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'government'}</t>
+          <t>government</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Government'}</t>
+          <t>Government</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manual_check'}</t>
+          <t>manual_check</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manual Check'}</t>
+          <t>Manual Check</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'automatic_check'}</t>
+          <t>automatic_check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Automatic Check'}</t>
+          <t>Automatic Check</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'verified'}</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Verified'}</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
